--- a/tiflow/audit-event-profile/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -379,6 +379,18 @@
   </si>
   <si>
     <t>79275</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FEATURE</t>
+  </si>
+  <si>
+    <t>79268</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FLOWTYPE</t>
+  </si>
+  <si>
+    <t>79270</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-chargeitem-operation-outcome-details-cs</t>
@@ -844,7 +856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1439,6 +1451,32 @@
         <v>119</v>
       </c>
       <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E47" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1469,7 +1507,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1486,66 +1524,66 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1578,7 +1616,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1595,40 +1633,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1661,7 +1699,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1678,105 +1716,105 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1809,7 +1847,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1826,40 +1864,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1892,7 +1930,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1909,53 +1947,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1988,7 +2026,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2005,118 +2043,118 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E11" s="2"/>
     </row>
